--- a/results/05-2026/beta/contributions-comparison-05-2026.xlsx
+++ b/results/05-2026/beta/contributions-comparison-05-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">federal_other_vulnerable_arp_contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal_student_loans_contribution</t>
   </si>
   <si>
     <t xml:space="preserve">state_subsidies_contribution</t>
@@ -634,13 +637,16 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -697,45 +703,48 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.00000824561118694087</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.0335089344402273</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-0.065417829213983</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.185757421025787</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0.241636630113166</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-0.0917203334476128</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>0.133565386955577</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.0419897826631274</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-0.0917203334476128</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.46938383380208</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.577601160588483</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -753,7 +762,7 @@
         <v>0.0488379551020667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.104919497398701</v>
+        <v>0.0128552657625797</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -792,45 +801,48 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.124466550251368</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.00000986356452146503</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.372769979146812</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-0.160080769289425</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>3.8369353291202</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>-2.39722668676711</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0.310013322726237</v>
-      </c>
       <c r="AA3" t="n">
-        <v>8.6385202038646</v>
+        <v>0.218260041490563</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.90337703978357</v>
+        <v>8.74486573546583</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.310013322726237</v>
+        <v>8.9309395294461</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.3430856821367</v>
+        <v>0.218260041490563</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.00272258447623</v>
+        <v>10.3706481717992</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.00961320689186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -848,7 +860,7 @@
         <v>0.0790187713359683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.239478027765301</v>
+        <v>0.0143221335174119</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -887,45 +899,48 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0.199552742055976</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.0000638572111890291</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.248951251691522</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-0.0421729893599904</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>-1.63537359312616</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.064635955563641</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0.776553839630428</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4.96965012385782</v>
+        <v>0.552346472186169</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.71579051059977</v>
+        <v>5.16139327319511</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.776553839630428</v>
+        <v>5.69127333718764</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.01578096190997</v>
+        <v>0.552346472186169</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.83723454465256</v>
+        <v>3.99126378849784</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.83799587371516</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -943,7 +958,7 @@
         <v>-0.182435353405305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.170924495989197</v>
+        <v>0.0109469268007227</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -982,45 +997,48 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.137038091934644</v>
+      </c>
+      <c r="V5" t="n">
         <v>-0.0000329691175003333</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.384174159984565</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-0.176484339194978</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-0.331735217356747</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0.0660050770494209</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-0.407827476320579</v>
-      </c>
       <c r="AA5" t="n">
-        <v>-2.49294901262296</v>
+        <v>-0.568772712361355</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.91133777497692</v>
+        <v>-2.35235872955152</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.407827476320579</v>
+        <v>-2.93502940425967</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.17706791528425</v>
+        <v>-0.568772712361355</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.91279564064112</v>
+        <v>-3.200759544567</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.90763406238303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -1038,7 +1056,7 @@
         <v>0.040191811227022</v>
       </c>
       <c r="H6" t="n">
-        <v>0.164621715306164</v>
+        <v>-0.0146310491062612</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1077,45 +1095,48 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0.127466485750547</v>
+      </c>
+      <c r="V6" t="n">
         <v>0.00181557790265906</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.228447862578173</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.0456274330040622</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.35163182855064</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.572864868349367</v>
       </c>
-      <c r="Z6" t="n">
-        <v>-0.0137788292063654</v>
-      </c>
       <c r="AA6" t="n">
-        <v>7.81623210851637</v>
+        <v>-0.193345941150108</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.80352438310025</v>
+        <v>7.93378769759511</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0137788292063654</v>
+        <v>7.75569645454409</v>
       </c>
       <c r="AD6" t="n">
-        <v>8.58229134330153</v>
+        <v>-0.193345941150108</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.94102251801598</v>
+        <v>8.53446341474537</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.92390395761885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -1133,7 +1154,7 @@
         <v>0.0169408295689168</v>
       </c>
       <c r="H7" t="n">
-        <v>0.179636342636072</v>
+        <v>-0.0379640320507537</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1172,45 +1193,48 @@
         <v>0.138666598140122</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0702033823773491</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.00768650492141917</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.13831785472286</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.257610701467474</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>-0.287610782304056</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>-0.92297475522981</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-0.0288747739188315</v>
-      </c>
       <c r="AA7" t="n">
-        <v>-1.08052926851467</v>
+        <v>-0.24689103402653</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.10968910356623</v>
+        <v>-1.00963271046716</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0288747739188315</v>
+        <v>-1.25880069434664</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.3202746411001</v>
+        <v>-0.24689103402653</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.77518243720679</v>
+        <v>-2.46938623188051</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.71389535669892</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -1228,7 +1252,7 @@
         <v>0.0303190711719823</v>
       </c>
       <c r="H8" t="n">
-        <v>0.154002401080685</v>
+        <v>-0.0425207530530465</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1267,45 +1291,48 @@
         <v>0.142944627710033</v>
       </c>
       <c r="U8" t="n">
+        <v>0.029074626310537</v>
+      </c>
+      <c r="V8" t="n">
         <v>-0.00122944518445003</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.0605652903172054</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.0643627476458901</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-0.610993309907876</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>-0.29456517846256</v>
       </c>
-      <c r="Z8" t="n">
-        <v>-0.118092063560072</v>
-      </c>
       <c r="AA8" t="n">
-        <v>-2.09082065057731</v>
+        <v>-0.31515314337929</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.21138431677861</v>
+        <v>-2.06113735720888</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.118092063560072</v>
+        <v>-2.38279100305357</v>
       </c>
       <c r="AD8" t="n">
-        <v>-3.11694280514905</v>
+        <v>-0.31515314337929</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.0079985045579658</v>
+        <v>-3.28834949142401</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.106007963281536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -1323,7 +1350,7 @@
         <v>0.0655390793395653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.154903020368478</v>
+        <v>-0.0475026428300258</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1362,45 +1389,48 @@
         <v>0.15386764165396</v>
       </c>
       <c r="U9" t="n">
+        <v>0.0257986939403195</v>
+      </c>
+      <c r="V9" t="n">
         <v>-0.00060286888446617</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-0.0231810529779638</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>-0.028599393048954</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.329994696071855</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.72933199543321</v>
       </c>
-      <c r="Z9" t="n">
-        <v>-0.00606153509630423</v>
-      </c>
       <c r="AA9" t="n">
-        <v>-2.44734167709947</v>
+        <v>-0.208789857580898</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.45354933045972</v>
+        <v>-2.42092105160786</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00606153509630423</v>
+        <v>-2.63468816179706</v>
       </c>
       <c r="AD9" t="n">
-        <v>-2.85288662982108</v>
+        <v>-0.208789857580898</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0730468168078258</v>
+        <v>-3.03402546115842</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.0643244424293917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -1418,7 +1448,7 @@
         <v>-0.0585793509828508</v>
       </c>
       <c r="H10" t="n">
-        <v>0.126940956615399</v>
+        <v>-0.0636914765269768</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1457,45 +1487,48 @@
         <v>0.129849330467061</v>
       </c>
       <c r="U10" t="n">
+        <v>0.0143072227949861</v>
+      </c>
+      <c r="V10" t="n">
         <v>-0.000669126063992638</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>0.0442724220334607</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>-0.090904806150079</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.328141854263953</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>-0.593660211068666</v>
       </c>
-      <c r="Z10" t="n">
-        <v>-0.683862139933784</v>
-      </c>
       <c r="AA10" t="n">
-        <v>-2.18260935157057</v>
+        <v>-0.876075859460641</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.88166727759111</v>
+        <v>-2.16798383433384</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.683862139933784</v>
+        <v>-3.06339026497288</v>
       </c>
       <c r="AD10" t="n">
-        <v>-3.80346934292373</v>
+        <v>-0.876075859460641</v>
       </c>
       <c r="AE10" t="n">
-        <v>-3.02339335474849</v>
+        <v>-3.9851923303055</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-3.19423837869211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -1513,7 +1546,7 @@
         <v>-0.214664512569586</v>
       </c>
       <c r="H11" t="n">
-        <v>0.129024188762039</v>
+        <v>-0.0803342153487852</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1552,45 +1585,48 @@
         <v>0.0888286293902712</v>
       </c>
       <c r="U11" t="n">
+        <v>-0.0170524557288868</v>
+      </c>
+      <c r="V11" t="n">
         <v>-0.000823667305731244</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>-0.0682460391169559</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>-0.0603932141150797</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.369773746805842</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>-1.03787566757402</v>
       </c>
-      <c r="Z11" t="n">
-        <v>-0.993989950231089</v>
-      </c>
       <c r="AA11" t="n">
-        <v>-3.10202058067492</v>
+        <v>-1.20568398792863</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.12645091476793</v>
+        <v>-3.11959610857322</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.993989950231089</v>
+        <v>-4.36239862308495</v>
       </c>
       <c r="AD11" t="n">
-        <v>-4.79455283553611</v>
+        <v>-1.20568398792863</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.64196290335749</v>
+        <v>-5.03050054385313</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-3.83451695668526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -1608,7 +1644,7 @@
         <v>0.0496954101018784</v>
       </c>
       <c r="H12" t="n">
-        <v>0.117940604485256</v>
+        <v>-0.0802162167568417</v>
       </c>
       <c r="I12" t="n">
         <v>0.0769149503246465</v>
@@ -1647,45 +1683,48 @@
         <v>0.051777688642237</v>
       </c>
       <c r="U12" t="n">
+        <v>-0.0117706301818196</v>
+      </c>
+      <c r="V12" t="n">
         <v>-0.000123762004087371</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.0527845221121613</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>-0.0495107428308193</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-0.614947240942878</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>0.478577805173849</v>
       </c>
-      <c r="Z12" t="n">
-        <v>-0.381400486763364</v>
-      </c>
       <c r="AA12" t="n">
-        <v>-1.71429964147729</v>
+        <v>-0.580579627213782</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.10242844734256</v>
+        <v>-1.72627805103759</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.458315437088011</v>
+        <v>-2.31716754988747</v>
       </c>
       <c r="AD12" t="n">
-        <v>-2.23879788311159</v>
+        <v>-0.657494577538429</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.42242667284813</v>
+        <v>-2.4535369856565</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-3.62581383024339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -1703,7 +1742,7 @@
         <v>0.13817168563911</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0947484661096629</v>
+        <v>-0.0662309339104978</v>
       </c>
       <c r="I13" t="n">
         <v>0.0497535662897082</v>
@@ -1742,45 +1781,48 @@
         <v>-0.036091410141793</v>
       </c>
       <c r="U13" t="n">
+        <v>-0.0106794377000554</v>
+      </c>
+      <c r="V13" t="n">
         <v>-0.000109722496949621</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0.00411887924544264</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.0875326979593281</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>-0.268021120898531</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>0.544630454339372</v>
       </c>
-      <c r="Z13" t="n">
-        <v>-0.311177364892391</v>
-      </c>
       <c r="AA13" t="n">
-        <v>-0.443693965838321</v>
+        <v>-0.282595033045533</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.756321378658227</v>
+        <v>-0.45442319460995</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.360930931182099</v>
+        <v>-0.73836697138364</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.479712045217387</v>
+        <v>-0.332348599335242</v>
       </c>
       <c r="AE13" t="n">
-        <v>-2.8291330266972</v>
+        <v>-0.4617576379428</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-2.98274687443948</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -1798,7 +1840,7 @@
         <v>0.142414615890442</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.114921618163856</v>
+        <v>-0.086884822835906</v>
       </c>
       <c r="I14" t="n">
         <v>0.352688858412503</v>
@@ -1837,45 +1879,48 @@
         <v>-0.092457615134267</v>
       </c>
       <c r="U14" t="n">
+        <v>-0.0104974524138563</v>
+      </c>
+      <c r="V14" t="n">
         <v>-0.000311140436700266</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0.0460597523323344</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.0995642627388841</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>-0.0628285716925441</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>0.323047488988425</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0.791069014271982</v>
-      </c>
       <c r="AA14" t="n">
-        <v>-1.24218523157011</v>
+        <v>0.818846407620433</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.441088882980743</v>
+        <v>-1.25281556342879</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.43838015585948</v>
+        <v>-0.423500585246295</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.180869965684862</v>
+        <v>0.46615754920793</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.92348318238749</v>
+        <v>-0.163281667950414</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-2.02726920885071</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -1893,7 +1938,7 @@
         <v>0.20744084444904</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2046841837829</v>
+        <v>-0.0799994595193902</v>
       </c>
       <c r="I15" t="n">
         <v>0.234874630908832</v>
@@ -1932,45 +1977,48 @@
         <v>-0.0966840653399767</v>
       </c>
       <c r="U15" t="n">
+        <v>-0.00875374801846945</v>
+      </c>
+      <c r="V15" t="n">
         <v>-0.000901417786342305</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>0.148467345637757</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.103560064389503</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>-0.268486583650671</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>0.37675672507515</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0.639354121972862</v>
-      </c>
       <c r="AA15" t="n">
-        <v>-1.38234978467433</v>
+        <v>0.762928566953573</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.733672388302574</v>
+        <v>-1.39123103603504</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.404479491064031</v>
+        <v>-0.617103421087763</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.625402246878095</v>
+        <v>0.528053936044742</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.881195535222982</v>
+        <v>-0.508833279663284</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.89685239280325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -1988,7 +2036,7 @@
         <v>0.11855270408997</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.208276940606983</v>
+        <v>-0.056916093561604</v>
       </c>
       <c r="I16" t="n">
         <v>0.230313539714713</v>
@@ -2027,45 +2075,48 @@
         <v>-0.0966627805616126</v>
       </c>
       <c r="U16" t="n">
+        <v>-0.138607631498054</v>
+      </c>
+      <c r="V16" t="n">
         <v>-0.0000746366255718586</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>-0.103313938667222</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>0.243113207232247</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>-0.172354520046453</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>0.600636706337094</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0.261410031122298</v>
-      </c>
       <c r="AA16" t="n">
-        <v>-0.656622075925647</v>
+        <v>0.412030542300483</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.393422525520161</v>
+        <v>-0.796177903897253</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0310964914075849</v>
+        <v>-0.380727188578476</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0348596607704799</v>
+        <v>0.18171700258577</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.312781149252465</v>
+        <v>0.047554997712165</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.271579396961083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -2083,7 +2134,7 @@
         <v>0.0713566379112017</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.208899806329515</v>
+        <v>-0.0695617412404508</v>
       </c>
       <c r="I17" t="n">
         <v>0.0818676169398049</v>
@@ -2122,45 +2173,48 @@
         <v>-0.096959286606789</v>
       </c>
       <c r="U17" t="n">
+        <v>-0.113129553553935</v>
+      </c>
+      <c r="V17" t="n">
         <v>-0.0000545598146086757</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.0367521777136748</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.0702317523530833</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>0.250026258743084</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>0.0879435617326674</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0.0291188192368216</v>
-      </c>
       <c r="AA17" t="n">
-        <v>-0.662422579376793</v>
+        <v>0.168106654503534</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.633099826986112</v>
+        <v>-0.776344234660777</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0527487977029832</v>
+        <v>-0.60685770938353</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.29513000651036</v>
+        <v>0.0862390375637294</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.266635639575708</v>
+        <v>-0.268887888907778</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.223361959702328</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -2178,7 +2232,7 @@
         <v>0.226257619100136</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.214603808595183</v>
+        <v>-0.0583421771791422</v>
       </c>
       <c r="I18" t="n">
         <v>0.126429969506553</v>
@@ -2217,45 +2271,48 @@
         <v>-0.063526397197148</v>
       </c>
       <c r="U18" t="n">
+        <v>-0.104799481735209</v>
+      </c>
+      <c r="V18" t="n">
         <v>-0.000591101276562183</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>-0.15853006033471</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.127457693502973</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>-1.32256837936611</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.26152887840551</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0.631414809003844</v>
-      </c>
       <c r="AA18" t="n">
-        <v>-0.454576284540892</v>
+        <v>0.78628460647213</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.179865143602601</v>
+        <v>-0.559877459260424</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.504984839497291</v>
+        <v>0.231049610408206</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.118825642642</v>
+        <v>0.659854636965577</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.191711737493993</v>
+        <v>0.170010109447605</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.140039015352823</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -2273,7 +2330,7 @@
         <v>0.196826924579495</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.225123402921256</v>
+        <v>-0.0450770336700762</v>
       </c>
       <c r="I19" t="n">
         <v>0.0936476749635413</v>
@@ -2312,45 +2369,48 @@
         <v>-0.0503808377656664</v>
       </c>
       <c r="U19" t="n">
+        <v>-0.096310570246564</v>
+      </c>
+      <c r="V19" t="n">
         <v>-0.0021680855276638</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>-0.124825687677082</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>0.109836183969317</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>0.176065602310738</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>-0.0553303248199536</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0.423527566669466</v>
-      </c>
       <c r="AA19" t="n">
-        <v>-0.384207077760455</v>
+        <v>0.602362580528956</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0410112570065093</v>
+        <v>-0.48090178331643</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.329879891705925</v>
+        <v>0.12447112969564</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.161746534497293</v>
+        <v>0.508714905565415</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.00507545784985447</v>
+        <v>0.245206407186424</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.048470906359604</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -2368,7 +2428,7 @@
         <v>0.0350150955007453</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.218516467472156</v>
+        <v>-0.0420529614264801</v>
       </c>
       <c r="I20" t="n">
         <v>-0.0944311286144539</v>
@@ -2407,45 +2467,48 @@
         <v>-0.0440281009267043</v>
       </c>
       <c r="U20" t="n">
+        <v>-0.0553398426809612</v>
+      </c>
+      <c r="V20" t="n">
         <v>-0.0000481981319541984</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>0.192074034349464</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>0.0420686719463712</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>0.624276286028791</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>-0.128951184598474</v>
       </c>
-      <c r="Z20" t="n">
-        <v>0.00433208961806812</v>
-      </c>
       <c r="AA20" t="n">
-        <v>-0.01888745513281</v>
+        <v>0.180384979214747</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.0145545091632898</v>
+        <v>-0.0742382360498926</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.098763218232522</v>
+        <v>0.106286927910456</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.480770592267026</v>
+        <v>0.274816107829201</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.116553190723991</v>
+        <v>0.601612029340773</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.186985164266756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -2463,7 +2526,7 @@
         <v>0.0391411302137562</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.219970219961965</v>
+        <v>-0.0330895642945137</v>
       </c>
       <c r="I21" t="n">
         <v>-0.134337351020563</v>
@@ -2502,45 +2565,48 @@
         <v>-0.0265684363093117</v>
       </c>
       <c r="U21" t="n">
+        <v>-0.0302912288977294</v>
+      </c>
+      <c r="V21" t="n">
         <v>-0.0000584549268793934</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>0.138952681402228</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>0.148998237211467</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>0.145302284954125</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>-0.00629483791547873</v>
       </c>
-      <c r="Z21" t="n">
-        <v>-0.0177897953990833</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0.234191950358427</v>
+        <v>0.168699850674615</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.216445388165571</v>
+        <v>0.203974334374208</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.11654755562148</v>
+        <v>0.37231700923784</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.355452835204218</v>
+        <v>0.303037201695179</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.279198901152636</v>
+        <v>0.511324456276486</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.382038250562822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -2558,7 +2624,7 @@
         <v>0.056172172525477</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.188746888483817</v>
+        <v>-0.00295807996764376</v>
       </c>
       <c r="I22" t="n">
         <v>-0.115307261317255</v>
@@ -2597,45 +2663,48 @@
         <v>-0.0106418570513199</v>
       </c>
       <c r="U22" t="n">
+        <v>-0.0297652241785434</v>
+      </c>
+      <c r="V22" t="n">
         <v>-0.000305138334205149</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>0.0925385175650943</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>0.000551965031565569</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>-0.993610612244152</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>0.400332757045023</v>
       </c>
-      <c r="Z22" t="n">
-        <v>-0.283369016326136</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0.0253809191774514</v>
+        <v>-0.0973949910447126</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.257912167048449</v>
+        <v>-0.00437632570967921</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.168061755008881</v>
+        <v>-0.101775817864685</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.851190022247578</v>
+        <v>0.0179122702725422</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.036694984930241</v>
+        <v>-0.695053673063814</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.165772304934967</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -2653,7 +2722,7 @@
         <v>-0.0393993485224859</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.192841980151365</v>
+        <v>0.0070494530187146</v>
       </c>
       <c r="I23" t="n">
         <v>0.216923374445816</v>
@@ -2692,45 +2761,48 @@
         <v>-0.0100206453912311</v>
       </c>
       <c r="U23" t="n">
+        <v>-0.0233356501478242</v>
+      </c>
+      <c r="V23" t="n">
         <v>-0.00103802633880351</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>0.285091465526087</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>-0.0299392802978311</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>-0.937821968966787</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.531980090246069</v>
       </c>
-      <c r="Z23" t="n">
-        <v>-0.475010062638365</v>
-      </c>
       <c r="AA23" t="n">
-        <v>0.469120272922062</v>
+        <v>-0.274529505412121</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.203555691108441</v>
+        <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.69193343708418</v>
+        <v>-0.0273475251368821</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.609397569829158</v>
+        <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.156091041151372</v>
+        <v>-0.4331894038576</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.00382664782603898</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -2748,7 +2820,7 @@
         <v>-0.014530714174193</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0667857677015623</v>
+        <v>0.126456632364786</v>
       </c>
       <c r="I24" t="n">
         <v>0.233931922438709</v>
@@ -2787,45 +2859,48 @@
         <v>-0.0086306387520275</v>
       </c>
       <c r="U24" t="n">
+        <v>-0.0297549970186519</v>
+      </c>
+      <c r="V24" t="n">
         <v>-0.0000539507371187338</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>0.316532912689999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.0465164147221872</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>0.273885378533513</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>-0.275751448037125</v>
       </c>
-      <c r="Z24" t="n">
-        <v>-0.333003537188347</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0.430455500008955</v>
+        <v>-0.139229581720164</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.0989348717429549</v>
+        <v>0.400833075000047</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.566935459627056</v>
+        <v>0.262180996866793</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0970688022393427</v>
+        <v>-0.373161504158873</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.252016488658293</v>
+        <v>0.26031492736318</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -2882,45 +2957,48 @@
         <v>-0.0076726144240776</v>
       </c>
       <c r="U25" t="n">
+        <v>-0.0242646124776583</v>
+      </c>
+      <c r="V25" t="n">
         <v>-0.0000531438557844164</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>0.283001238493291</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>0.0427711776553399</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>-1.57957660760554</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>0.261833944831957</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>-0.236364588453239</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0.353220653663715</v>
-      </c>
       <c r="AB25" t="n">
-        <v>0.117735835959556</v>
+        <v>0.329046389863244</v>
       </c>
       <c r="AC25" t="n">
+        <v>0.0935013261067523</v>
+      </c>
+      <c r="AD25" t="n">
         <v>-0.378847726241531</v>
       </c>
-      <c r="AD25" t="n">
-        <v>-1.20000682681403</v>
-      </c>
       <c r="AE25" t="n">
-        <v>-0.640881404162854</v>
+        <v>-1.22424133666683</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.523042371556266</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" t="n">
         <v>-1</v>
@@ -2977,45 +3055,48 @@
         <v>-0.00724537368698469</v>
       </c>
       <c r="U26" t="n">
+        <v>-0.00124806099192601</v>
+      </c>
+      <c r="V26" t="n">
         <v>-0.0000704209155706835</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>0.220373616310185</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>-0.0059703885150818</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>-0.259566169530045</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.619858406339934</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.513339321470254</v>
       </c>
-      <c r="AA26" t="n">
-        <v>-0.0945012120602486</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0.47934325761517</v>
+        <v>-0.0957505000997191</v>
       </c>
       <c r="AC26" t="n">
+        <v>0.478100646433021</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.199370273601759</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0.839635494425059</v>
-      </c>
       <c r="AE26" t="n">
-        <v>-0.218175024994695</v>
+        <v>0.838392883242911</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.139680732479585</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -3072,45 +3153,48 @@
         <v>-0.00646590322831928</v>
       </c>
       <c r="U27" t="n">
+        <v>-0.00308722385724039</v>
+      </c>
+      <c r="V27" t="n">
         <v>-0.000502009882075564</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.181472014367723</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.0198469524294004</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>-0.567974729331849</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>0.144226151387002</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>0.502600841854134</v>
       </c>
-      <c r="AA27" t="n">
-        <v>-0.191289588691957</v>
-      </c>
       <c r="AB27" t="n">
-        <v>0.372318810025706</v>
+        <v>-0.19438299598541</v>
       </c>
       <c r="AC27" t="n">
+        <v>0.369241690759268</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.25076637782819</v>
       </c>
-      <c r="AD27" t="n">
-        <v>-0.0514297679191404</v>
-      </c>
       <c r="AE27" t="n">
-        <v>-0.0786830745171904</v>
+        <v>-0.0545068871855782</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.0450101033115796</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
         <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>58</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3167,45 +3251,48 @@
         <v>-0.00574771421528885</v>
       </c>
       <c r="U28" t="n">
+        <v>0.00426556737716453</v>
+      </c>
+      <c r="V28" t="n">
         <v>-0.000427434693273484</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>0.137106273050434</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>-0.0452687741177263</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>-0.320692545073825</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>-0.161848243652142</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>0.265630291381617</v>
       </c>
-      <c r="AA28" t="n">
-        <v>-0.105948447441316</v>
-      </c>
       <c r="AB28" t="n">
-        <v>0.219977889128903</v>
+        <v>-0.10167812826666</v>
       </c>
       <c r="AC28" t="n">
+        <v>0.224236278137344</v>
+      </c>
+      <c r="AD28" t="n">
         <v>0.187609561690159</v>
       </c>
-      <c r="AD28" t="n">
-        <v>-0.262562899597064</v>
-      </c>
       <c r="AE28" t="n">
-        <v>-0.168590999976292</v>
+        <v>-0.258304510588623</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.17466496279953</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -3262,45 +3349,48 @@
         <v>-0.00316815333426748</v>
       </c>
       <c r="U29" t="n">
+        <v>0.00864153470503527</v>
+      </c>
+      <c r="V29" t="n">
         <v>-0.000395632535644162</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.0857902637573375</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>-0.0329022460380169</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>-0.144265791295202</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>-0.162098951525747</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>-0.0468776240724925</v>
       </c>
-      <c r="AA29" t="n">
-        <v>-0.0791480720390094</v>
-      </c>
       <c r="AB29" t="n">
-        <v>-0.0660648375760431</v>
+        <v>-0.0704993211970471</v>
       </c>
       <c r="AC29" t="n">
+        <v>-0.0574118101570617</v>
+      </c>
+      <c r="AD29" t="n">
         <v>0.00547447060960826</v>
       </c>
-      <c r="AD29" t="n">
-        <v>-0.372429580396992</v>
-      </c>
       <c r="AE29" t="n">
-        <v>0.0383033116279667</v>
+        <v>-0.363776552978011</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.0404512331226745</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -3357,45 +3447,48 @@
         <v>-0.00178156742611225</v>
       </c>
       <c r="U30" t="n">
+        <v>0.00237696736883962</v>
+      </c>
+      <c r="V30" t="n">
         <v>-0.000366120190757605</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>0.0517725184405778</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.00717628862688768</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>-0.138693989964264</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>-0.160990106187987</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>-0.51984196881698</v>
       </c>
-      <c r="AA30" t="n">
-        <v>0.0334113122146709</v>
-      </c>
       <c r="AB30" t="n">
-        <v>-0.426246898977315</v>
+        <v>0.0357874385826148</v>
       </c>
       <c r="AC30" t="n">
+        <v>-0.42385770341375</v>
+      </c>
+      <c r="AD30" t="n">
         <v>-0.252659270881237</v>
       </c>
-      <c r="AD30" t="n">
-        <v>-0.725930995129566</v>
-      </c>
       <c r="AE30" t="n">
-        <v>-0.353088310760689</v>
+        <v>-0.723541799566001</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.350032437579553</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -3452,45 +3545,48 @@
         <v>-0.00149913222094544</v>
       </c>
       <c r="U31" t="n">
+        <v>-0.000324228727302213</v>
+      </c>
+      <c r="V31" t="n">
         <v>-0.000318826753313223</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.0605267521181745</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>-0.0155118321226031</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>-0.121186203903832</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>-0.156665011648983</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>-0.470137339793632</v>
       </c>
-      <c r="AA31" t="n">
-        <v>0.0358113621335527</v>
-      </c>
       <c r="AB31" t="n">
-        <v>-0.374147429438606</v>
+        <v>0.03548725664359</v>
       </c>
       <c r="AC31" t="n">
+        <v>-0.37447315095468</v>
+      </c>
+      <c r="AD31" t="n">
         <v>-0.105893959920281</v>
       </c>
-      <c r="AD31" t="n">
-        <v>-0.651998644991421</v>
-      </c>
       <c r="AE31" t="n">
-        <v>-0.50323053002876</v>
+        <v>-0.652324366507495</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.499486807410033</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3547,45 +3643,48 @@
         <v>-0.00123904239793884</v>
       </c>
       <c r="U32" t="n">
+        <v>0.00504321126838243</v>
+      </c>
+      <c r="V32" t="n">
         <v>-0.000312517607016392</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.0102429996730462</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.0243680184013916</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>-0.126639213309576</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>-0.165088104409586</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>-0.247426180026452</v>
       </c>
-      <c r="AA32" t="n">
-        <v>-0.0451843112530229</v>
-      </c>
       <c r="AB32" t="n">
-        <v>-0.292728985472978</v>
+        <v>-0.0401386836773411</v>
       </c>
       <c r="AC32" t="n">
+        <v>-0.287670126863767</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.139450228992291</v>
       </c>
-      <c r="AD32" t="n">
-        <v>-0.584456303192139</v>
-      </c>
       <c r="AE32" t="n">
-        <v>-0.583703880927529</v>
+        <v>-0.579397444582929</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.579760040908609</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3642,45 +3741,48 @@
         <v>-0.000240277352383458</v>
       </c>
       <c r="U33" t="n">
+        <v>0.00394550427927945</v>
+      </c>
+      <c r="V33" t="n">
         <v>-0.000305845153127051</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.0550834289509777</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>-0.0112608000960554</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>-0.193154801650048</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>-0.162508973770544</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.249695769869229</v>
       </c>
-      <c r="AA33" t="n">
-        <v>0.0152909029347207</v>
-      </c>
       <c r="AB33" t="n">
-        <v>-0.234364347345436</v>
+        <v>0.0192357666668917</v>
       </c>
       <c r="AC33" t="n">
+        <v>-0.230409029704535</v>
+      </c>
+      <c r="AD33" t="n">
         <v>0.179517283326634</v>
       </c>
-      <c r="AD33" t="n">
-        <v>-0.590028122766028</v>
-      </c>
       <c r="AE33" t="n">
-        <v>-0.638103516519787</v>
+        <v>-0.586072805125127</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.635334103945388</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3737,37 +3839,40 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>-0.000299774451181366</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.077764056217266</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.0094510056392769</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>-0.225455437068654</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>-0.162252828276773</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>-0.604501734527056</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>-0.0389810176841416</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>-0.643732556992063</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>0.0130884270769487</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>-1.03144082233749</v>
       </c>
-      <c r="AE34" t="n">
-        <v>-0.714480973321769</v>
+      <c r="AF34" t="n">
+        <v>-0.712308859638261</v>
       </c>
     </row>
   </sheetData>
@@ -3875,13 +3980,16 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -3938,45 +4046,48 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.00000824561118694087</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.0335089344402273</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-0.065417829213983</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.185757421025787</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0.241636630113166</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-0.0917203334476128</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>0.133565386955577</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.0419897826631274</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-0.0917203334476128</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.46938383380208</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.577601160588483</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -4033,45 +4144,48 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.124466550251368</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.00000986356452146503</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.372769979146812</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-0.160080769289425</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>3.8369353291202</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>-2.39722668676711</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.218260041490563</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>8.74486573546583</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>8.9309395294461</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.218260041490563</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>10.3706481717992</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>3.00961320689186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
@@ -4128,45 +4242,48 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0.199552742055976</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.0000638572111890291</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.248951251691522</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-0.0421729893599904</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>-1.63537359312616</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.064635955563641</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>0.552346472186169</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>5.16139327319511</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>5.69127333718764</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>0.552346472186169</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>3.99126378849784</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>3.83799587371516</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
         <v>-1</v>
@@ -4223,45 +4340,48 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.137038091934644</v>
+      </c>
+      <c r="V5" t="n">
         <v>-0.0000329691175003333</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.384174159984565</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-0.176484339194978</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-0.331735217356747</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0.0660050770494209</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.568772712361355</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>-2.35235872955152</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>-2.93502940425967</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.568772712361355</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-3.200759544567</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>2.90763406238303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="n">
         <v>-1</v>
@@ -4318,45 +4438,48 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0.127466485750547</v>
+      </c>
+      <c r="V6" t="n">
         <v>0.00181557790265906</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.228447862578173</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.0456274330040622</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.35163182855064</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.572864868349367</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.193345941150108</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>7.93378769759511</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>7.75569645454409</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-0.193345941150108</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>8.53446341474537</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>4.92390395761885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
         <v>-1</v>
@@ -4413,45 +4536,48 @@
         <v>0.138666598140122</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0702033823773491</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.00768650492141917</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.13831785472286</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.257610701467474</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>-0.287610782304056</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>-0.92297475522981</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.24689103402653</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>-1.00963271046716</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>-1.25880069434664</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-0.24689103402653</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>-2.46938623188051</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>1.71389535669892</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
         <v>-1</v>
@@ -4508,45 +4634,48 @@
         <v>0.142944627710033</v>
       </c>
       <c r="U8" t="n">
+        <v>0.029074626310537</v>
+      </c>
+      <c r="V8" t="n">
         <v>-0.00122944518445003</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.0605652903172054</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.0643627476458901</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-0.610993309907876</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>-0.29456517846256</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-0.31515314337929</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>-2.06113735720888</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-2.38279100305357</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-0.31515314337929</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-3.28834949142401</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>-0.106007963281536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
         <v>-1</v>
@@ -4603,45 +4732,48 @@
         <v>0.15386764165396</v>
       </c>
       <c r="U9" t="n">
+        <v>0.0257986939403195</v>
+      </c>
+      <c r="V9" t="n">
         <v>-0.00060286888446617</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-0.0231810529779638</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>-0.028599393048954</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.329994696071855</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.72933199543321</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.208789857580898</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>-2.42092105160786</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>-2.63468816179706</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-0.208789857580898</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>-3.03402546115842</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>-0.0643244424293917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>-1</v>
@@ -4698,45 +4830,48 @@
         <v>0.129849330467061</v>
       </c>
       <c r="U10" t="n">
+        <v>0.0143072227949861</v>
+      </c>
+      <c r="V10" t="n">
         <v>-0.000669126063992638</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>0.0442724220334607</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>-0.090904806150079</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.328141854263953</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>-0.593660211068666</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-0.876075859460641</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>-2.16798383433384</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>-3.06339026497288</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-0.876075859460641</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>-3.9851923303055</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>-3.19423837869211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
         <v>-1</v>
@@ -4793,45 +4928,48 @@
         <v>0.0888286293902712</v>
       </c>
       <c r="U11" t="n">
+        <v>-0.0170524557288868</v>
+      </c>
+      <c r="V11" t="n">
         <v>-0.000823667305731244</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>-0.0682460391169559</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>-0.0603932141150797</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.369773746805842</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>-1.03787566757402</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-1.20568398792863</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>-3.11959610857322</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>-4.36239862308495</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-1.20568398792863</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>-5.03050054385313</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>-3.83451695668526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>-1</v>
@@ -4888,45 +5026,48 @@
         <v>0.051777688642237</v>
       </c>
       <c r="U12" t="n">
+        <v>-0.0117706301818196</v>
+      </c>
+      <c r="V12" t="n">
         <v>-0.000123762004087371</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.0527845221121613</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>-0.0495107428308193</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-0.614947240942878</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>0.478577805173849</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>-0.580579627213782</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>-1.72627805103759</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>-2.31716754988747</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-0.657494577538429</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>-2.4535369856565</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>-3.62581383024339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>-1</v>
@@ -4983,45 +5124,48 @@
         <v>-0.036091410141793</v>
       </c>
       <c r="U13" t="n">
+        <v>-0.0106794377000554</v>
+      </c>
+      <c r="V13" t="n">
         <v>-0.000109722496949621</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0.00411887924544264</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.0875326979593281</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>-0.268021120898531</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>0.544630454339372</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-0.282595033045533</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>-0.45442319460995</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>-0.73836697138364</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>-0.332348599335242</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>-0.4617576379428</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>-2.98274687443948</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
         <v>-1</v>
@@ -5078,45 +5222,48 @@
         <v>-0.092457615134267</v>
       </c>
       <c r="U14" t="n">
+        <v>-0.0104974524138563</v>
+      </c>
+      <c r="V14" t="n">
         <v>-0.000311140436700266</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0.0460597523323344</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.0995642627388841</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>-0.0628285716925441</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>0.323047488988425</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>0.818846407620433</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>-1.25281556342879</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>-0.423500585246295</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>0.46615754920793</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>-0.163281667950414</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AF14" t="n">
         <v>-2.02726920885071</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="n">
         <v>-1</v>
@@ -5173,45 +5320,48 @@
         <v>-0.0966840653399767</v>
       </c>
       <c r="U15" t="n">
+        <v>-0.00875374801846945</v>
+      </c>
+      <c r="V15" t="n">
         <v>-0.000901417786342305</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>0.148467345637757</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.103560064389503</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>-0.268486583650671</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>0.37675672507515</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>0.762928566953573</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>-1.39123103603504</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>-0.617103421087763</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>0.528053936044742</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>-0.508833279663284</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AF15" t="n">
         <v>-0.89685239280325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
         <v>-1</v>
@@ -5268,45 +5418,48 @@
         <v>-0.0966627805616126</v>
       </c>
       <c r="U16" t="n">
+        <v>-0.138607631498054</v>
+      </c>
+      <c r="V16" t="n">
         <v>-0.0000746366255718586</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>-0.103313938667222</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>0.243113207232247</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>-0.172354520046453</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>0.600636706337094</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>0.412030542300483</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>-0.796177903897253</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>-0.380727188578476</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>0.18171700258577</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>0.047554997712165</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>-0.271579396961083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
         <v>-1</v>
@@ -5363,45 +5516,48 @@
         <v>-0.096959286606789</v>
       </c>
       <c r="U17" t="n">
+        <v>-0.113129553553935</v>
+      </c>
+      <c r="V17" t="n">
         <v>-0.0000545598146086757</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.0367521777136748</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.0702317523530833</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>0.250026258743084</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>0.0879435617326674</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>0.168106654503534</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>-0.776344234660777</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>-0.60685770938353</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>0.0862390375637294</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>-0.268887888907778</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>-0.223361959702328</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
         <v>-1</v>
@@ -5458,45 +5614,48 @@
         <v>-0.063526397197148</v>
       </c>
       <c r="U18" t="n">
+        <v>-0.104799481735209</v>
+      </c>
+      <c r="V18" t="n">
         <v>-0.000591101276562183</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>-0.15853006033471</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.127457693502973</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>-0.171780249704384</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>0.110740748743783</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>0.78628460647213</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>-0.559877459260424</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>0.231049610408206</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>0.659854636965577</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>0.170010109447605</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>-0.140039015352823</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
@@ -5553,45 +5712,48 @@
         <v>-0.0503808377656664</v>
       </c>
       <c r="U19" t="n">
+        <v>-0.096310570246564</v>
+      </c>
+      <c r="V19" t="n">
         <v>-0.0021680855276638</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>-0.124825687677082</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>0.109836183969317</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>0.166035250882516</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>-0.045299973391732</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>0.602362580528956</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>-0.48090178331643</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>0.12447112969564</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>0.508714905565415</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>0.245206407186424</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
         <v>0.048470906359604</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n">
         <v>-1</v>
@@ -5648,45 +5810,48 @@
         <v>-0.0440281009267043</v>
       </c>
       <c r="U20" t="n">
+        <v>-0.0553398426809612</v>
+      </c>
+      <c r="V20" t="n">
         <v>-0.0000481981319541984</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>0.192074034349464</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>0.0420686719463712</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>0.612848820878669</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>-0.117523719448353</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>0.180384979214747</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>-0.0742382360498926</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>0.106286927910456</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>0.274816107829201</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>0.601612029340773</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
         <v>0.186985164266756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
         <v>-1</v>
@@ -5743,45 +5908,48 @@
         <v>-0.0265684363093117</v>
       </c>
       <c r="U21" t="n">
+        <v>-0.0302912288977294</v>
+      </c>
+      <c r="V21" t="n">
         <v>-0.0000584549268793934</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>0.138952681402228</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>0.148998237211467</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>0.135250550861866</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.00375689617678003</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>0.168699850674615</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>0.203974334374208</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>0.37231700923784</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>0.303037201695179</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>0.511324456276486</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AF21" t="n">
         <v>0.382038250562822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
         <v>-1</v>
@@ -5838,45 +6006,48 @@
         <v>-0.0106418570513199</v>
       </c>
       <c r="U22" t="n">
+        <v>-0.0297652241785434</v>
+      </c>
+      <c r="V22" t="n">
         <v>-0.000305138334205149</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>0.0925385175650943</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>0.000551965031565569</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>-1.18817041587178</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>0.59489256067265</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>-0.0973949910447126</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>-0.00437632570967921</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>-0.101775817864685</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>0.0179122702725422</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>-0.695053673063814</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>0.165772304934967</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
         <v>-1</v>
@@ -5933,45 +6104,48 @@
         <v>-0.0100206453912311</v>
       </c>
       <c r="U23" t="n">
+        <v>-0.0233356501478242</v>
+      </c>
+      <c r="V23" t="n">
         <v>-0.00103802633880351</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>0.285091465526087</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>-0.0299392802978311</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>-0.945848277891172</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.540006399170454</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>-0.274529505412121</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>0.445899379286268</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>-0.0273475251368821</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>-0.491452879857937</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>-0.4331894038576</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AF23" t="n">
         <v>-0.00382664782603897</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" t="n">
         <v>-1</v>
@@ -6028,45 +6202,48 @@
         <v>-0.0086306387520275</v>
       </c>
       <c r="U24" t="n">
+        <v>-0.0297549970186519</v>
+      </c>
+      <c r="V24" t="n">
         <v>-0.0000539507371187338</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>0.316532912689999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.0465164147221872</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>0.259598704102414</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>-0.261464773606026</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>-0.139229581720164</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>0.400833075000047</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>0.262180996866793</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>-0.373161504158873</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>0.26031492736318</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
         <v>-1</v>
@@ -6123,45 +6300,48 @@
         <v>-0.0076726144240776</v>
       </c>
       <c r="U25" t="n">
+        <v>-0.0242646124776583</v>
+      </c>
+      <c r="V25" t="n">
         <v>-0.0000531438557844164</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>0.283001238493291</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>0.0427711776553399</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>-1.59047979678416</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>0.272737134010574</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>-0.270169588737866</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>0.329046389863244</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>0.0598134793214488</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>-0.412652726526158</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>-1.25792918345213</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AF25" t="n">
         <v>-0.531464333252592</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" t="n">
         <v>-1</v>
@@ -6218,45 +6398,48 @@
         <v>-0.00724609284152218</v>
       </c>
       <c r="U26" t="n">
+        <v>-0.00125291743599055</v>
+      </c>
+      <c r="V26" t="n">
         <v>-0.0000696617484409661</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>0.224985702190415</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>0.0124692193307716</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>0.299681722190402</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.0657687568511386</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.463404670727734</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>-0.0604293144674622</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>0.463266623529774</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>0.148888893636348</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
         <v>0.828717102571314</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AF26" t="n">
         <v>-0.15052163934381</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -6313,45 +6496,48 @@
         <v>-0.00645843383716623</v>
       </c>
       <c r="U27" t="n">
+        <v>-0.00308365752099749</v>
+      </c>
+      <c r="V27" t="n">
         <v>-0.000501429966115183</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.207022102238222</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>0.0365288260044681</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>-0.330545226387455</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>-0.0928836530179101</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>0.485607963229528</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>-0.0142040674807482</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>0.531476265418905</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>0.234064323299038</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>0.10804738601354</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>-0.0152124418760249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
         <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>58</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -6408,45 +6594,48 @@
         <v>-0.00574107447962623</v>
       </c>
       <c r="U28" t="n">
+        <v>0.00426063987336252</v>
+      </c>
+      <c r="V28" t="n">
         <v>-0.000426940925803921</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>0.162770134174828</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>-0.0273950236581683</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>-0.182706291067979</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>-0.139873044970078</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>0.255014185511323</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>0.0811831420485551</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>0.395979289544949</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>0.177083575542115</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>0.073399953506892</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AF28" t="n">
         <v>-0.061941185340097</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -6503,45 +6692,48 @@
         <v>-0.00316449350844382</v>
       </c>
       <c r="U29" t="n">
+        <v>0.00863155222093056</v>
+      </c>
+      <c r="V29" t="n">
         <v>-0.000395175505607586</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.110104285704918</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>-0.0142421131305181</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>-0.165982905043573</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>-0.140839771734219</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>-0.0600454191026175</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>0.104915517060876</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>0.104936634947096</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>-0.00775380490190472</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>-0.201886041830696</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AF29" t="n">
         <v>0.202069600065263</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -6598,45 +6790,48 @@
         <v>-0.00177950937707208</v>
       </c>
       <c r="U30" t="n">
+        <v>0.00237422153404077</v>
+      </c>
+      <c r="V30" t="n">
         <v>-0.000365697253103981</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>0.0747419360682316</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.00432257924151644</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>-0.1602387861888</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>-0.139951506095078</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>-0.533901846857373</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>0.18995088856399</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>-0.282876784788877</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>-0.267027899335481</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>-0.583067077072755</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AF30" t="n">
         <v>-0.150876444845755</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -6693,45 +6888,48 @@
         <v>-0.00149740043885975</v>
       </c>
       <c r="U31" t="n">
+        <v>-0.000323854182184991</v>
+      </c>
+      <c r="V31" t="n">
         <v>-0.000318458448563437</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.0602243053891414</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>-0.0135877228904138</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>-0.14208312752099</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>-0.136187107329353</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>-0.484036400696089</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>0.0706728660628411</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>-0.35300042447314</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>-0.120213984396549</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>-0.631270659323483</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AF31" t="n">
         <v>-0.335705956180011</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -6788,45 +6986,48 @@
         <v>-0.00123761106939872</v>
       </c>
       <c r="U32" t="n">
+        <v>0.00503738545094546</v>
+      </c>
+      <c r="V32" t="n">
         <v>-0.000312156590467466</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.0092716635034082</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.0234751031805249</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>-0.147016752572777</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>-0.145161352331443</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>-0.260600449467441</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>0.0195130068435475</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>-0.241033493505418</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>0.125828825912292</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
         <v>-0.533211598409638</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AF32" t="n">
         <v>-0.487358844159143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -6883,45 +7084,48 @@
         <v>-0.000239999786936005</v>
       </c>
       <c r="U33" t="n">
+        <v>0.00394094650479018</v>
+      </c>
+      <c r="V33" t="n">
         <v>-0.000305491844496977</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>-0.00136295384642158</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>-0.0115869753952157</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>-0.213430042513555</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>-0.143061358041577</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.247370645122349</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>-0.00912811548088149</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>-0.256522744217091</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>0.181346316904211</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>-0.613014144772223</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
         <v>-0.590140869894525</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -6978,36 +7182,39 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>-0.000299428155345378</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>-0.0331773637149976</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.00776152455226643</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>-0.245538348742651</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>-0.143181122174836</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>-0.59681672518361</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>-0.10280007135667</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>-0.700267708903581</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>0.0200594465950505</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>-1.08898717982107</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AF34" t="n">
         <v>-0.716620895581603</v>
       </c>
     </row>
@@ -7116,10 +7323,13 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="n">
@@ -7207,12 +7417,15 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="n">
@@ -7231,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0920642316361213</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -7285,27 +7498,30 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.091753281235674</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.10634553160123</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0275624896625306</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.091753281235674</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0275624896625004</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.00689062241562999</v>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
@@ -7324,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.225155894247889</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -7378,27 +7594,30 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.224207367444259</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.191743149337291</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0245171734121294</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.224207367444259</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0245171734121299</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.000761329062600069</v>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
@@ -7417,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.159977569188474</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7471,27 +7690,30 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.160945236040776</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.14059028307144</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0236916292827498</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.160945236040776</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0236916292827503</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.00516157825809005</v>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
@@ -7510,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.179252764412425</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7564,27 +7786,30 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.179567111943743</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.11755558907874</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0478279285561598</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.179567111943743</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0478279285561616</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0171185603971296</v>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
@@ -7603,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.217600374686826</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7657,27 +7882,30 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.218016260107699</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0708965580475098</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.14911159078041</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.218016260107699</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.14911159078041</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.06128708050787</v>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8"/>
       <c r="C8" t="n">
@@ -7696,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.196523154133732</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -7750,27 +7978,30 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.197061079819218</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.0296832933684303</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.17140668627496</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.197061079819218</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.17140668627496</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0980094587235702</v>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="n">
@@ -7789,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.202405663198504</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7843,27 +8074,30 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.202728322484594</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.02642062549161</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.18113883133734</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.202728322484594</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.18113883133734</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.137371259237217</v>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
@@ -7882,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.190632433142376</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -7936,27 +8170,30 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.192213719526857</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.01462551723673</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.18172298738177</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.192213719526857</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.18172298738177</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.17084502394362</v>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11"/>
       <c r="C11" t="n">
@@ -7975,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.209358404110824</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -8029,27 +8266,30 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.211694037697541</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0175755278982996</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.23594770831702</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.211694037697541</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.23594770831702</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.19255405332777</v>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12"/>
       <c r="C12" t="n">
@@ -8068,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.198156821242098</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -8122,27 +8362,30 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.199179140450418</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0119784095602999</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.21473910254491</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.199179140450418</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.21473910254491</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.20338715739526</v>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13"/>
       <c r="C13" t="n">
@@ -8161,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0285175321991651</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -8215,27 +8458,30 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.028582331846858</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.010729228771629</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.017954407274587</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.028582331846857</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.017954407274587</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.15361384774228</v>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14"/>
       <c r="C14" t="n">
@@ -8254,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02803679532795</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -8308,27 +8554,30 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.0277773933484511</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01063033185868</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.017588297734448</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.02777739334845</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.017588297734448</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.10378602646322</v>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15"/>
       <c r="C15" t="n">
@@ -8347,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.12468472426351</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8401,27 +8650,30 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.123574444980711</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.00888125136070994</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.116568967214811</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.123574444980711</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.116568967214811</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.015656857580268</v>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16"/>
       <c r="C16" t="n">
@@ -8440,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.151360847045379</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8494,27 +8746,30 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.150620511178185</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.139555827971606</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.012695336941685</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.150620511178185</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.0126953369416851</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.041201752291382</v>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
@@ -8533,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.139338065089064</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -8587,27 +8842,30 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.138987835266712</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.113921655283984</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.026242117602582</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.138987835266713</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.026242117602582</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.04327367987338</v>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
@@ -8626,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.156261631416041</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -8674,33 +8932,36 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>-1.15078812966173</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.15078812966173</v>
       </c>
-      <c r="Z18" t="n">
-        <v>-0.154869797468286</v>
-      </c>
       <c r="AA18" t="n">
-        <v>0.105301174719532</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.051184466805605</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.154869797468286</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.051184466805605</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.05167272214117</v>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
@@ -8719,7 +8980,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.18004636925118</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8767,33 +9028,36 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.010030351428222</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>-0.0100303514282216</v>
       </c>
-      <c r="Z19" t="n">
-        <v>-0.17883501385949</v>
-      </c>
       <c r="AA19" t="n">
-        <v>0.096694705555975</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.0834598726891307</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.17883501385949</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.083459872689131</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.0433954485097495</v>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
@@ -8812,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.176463506045676</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8860,33 +9124,36 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.0114274651501221</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>-0.011427465150121</v>
       </c>
-      <c r="Z20" t="n">
-        <v>-0.176052889596679</v>
-      </c>
       <c r="AA20" t="n">
-        <v>0.0553507809170826</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.120841437073746</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.176052889596679</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.120841437073747</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.070431973542765</v>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
@@ -8905,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.186880655667451</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -8953,33 +9220,36 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0.010051734092259</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>-0.0100517340922588</v>
       </c>
-      <c r="Z21" t="n">
-        <v>-0.186489646073698</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0.030217615984219</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.155871621072269</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.186489646073699</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.155871621072268</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.102839349410186</v>
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
@@ -8998,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.185788808516173</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -9046,33 +9316,36 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>0.194559803627628</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>-0.194559803627627</v>
       </c>
-      <c r="Z22" t="n">
-        <v>-0.185974025281423</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0.0297572448871306</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.156136349183764</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.185974025281423</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.156136349183764</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.129077320004726</v>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23"/>
       <c r="C23" t="n">
@@ -9091,7 +9364,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.19989143317008</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -9139,33 +9412,36 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.00802630892438494</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>-0.00802630892438505</v>
       </c>
-      <c r="Z23" t="n">
-        <v>-0.200480557226244</v>
-      </c>
       <c r="AA23" t="n">
-        <v>0.023220893635794</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.176208165971559</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.200480557226243</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.176208165971558</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.152264393325333</v>
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.00000000000000000997465998686664</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24"/>
       <c r="C24" t="n">
@@ -9184,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.193242400066348</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -9232,33 +9508,36 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.014286674431099</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>-0.014286674431099</v>
       </c>
-      <c r="Z24" t="n">
-        <v>-0.193773955468183</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0.029622425008908</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.163246125123838</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.193773955468183</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.163246125123837</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.162865565337856</v>
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25"/>
       <c r="C25" t="n">
@@ -9325,33 +9604,36 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.01090318917862</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>-0.010903189178617</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>0.033805000284627</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0.024174263800471</v>
-      </c>
       <c r="AB25" t="n">
-        <v>0.0579223566381072</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
+        <v>0.0336878467853035</v>
+      </c>
+      <c r="AD25" t="n">
         <v>0.033805000284627</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0.0579223566381</v>
-      </c>
       <c r="AE25" t="n">
-        <v>-0.109417070910262</v>
+        <v>0.0336878467852999</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.00842196169632603</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
@@ -9409,42 +9691,45 @@
         <v>0.000000719154537490163</v>
       </c>
       <c r="U26" t="n">
+        <v>0.00000485644406454004</v>
+      </c>
+      <c r="V26" t="n">
         <v>-0.000000759167129717398</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>-0.00461208588022999</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>-0.0184396078458534</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>-0.559247891720447</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.554089649488795</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.04993465074252</v>
       </c>
-      <c r="AA26" t="n">
-        <v>-0.0340718975927864</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0.016076634085396</v>
+        <v>-0.0353211856322569</v>
       </c>
       <c r="AC26" t="n">
+        <v>0.014834022903247</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.050481379965411</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0.010918391853745</v>
-      </c>
       <c r="AE26" t="n">
-        <v>-0.067653385650885</v>
+        <v>0.00967578067159691</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.010840906864225</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
@@ -9502,42 +9787,45 @@
         <v>-0.00000746939115305045</v>
       </c>
       <c r="U27" t="n">
+        <v>-0.00000356633624289983</v>
+      </c>
+      <c r="V27" t="n">
         <v>-0.000000579915960381011</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>-0.025550087870499</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>-0.0166818735750677</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>-0.237429502944394</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>0.237109804404912</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>0.016992878624606</v>
       </c>
-      <c r="AA27" t="n">
-        <v>-0.177085521211209</v>
-      </c>
       <c r="AB27" t="n">
-        <v>-0.159157455393199</v>
+        <v>-0.180178928504662</v>
       </c>
       <c r="AC27" t="n">
+        <v>-0.162234574659637</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.016702054529152</v>
       </c>
-      <c r="AD27" t="n">
-        <v>-0.15947715393268</v>
-      </c>
       <c r="AE27" t="n">
-        <v>-0.0634706326411655</v>
+        <v>-0.162554273199118</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.0297976614355547</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
@@ -9595,42 +9883,45 @@
         <v>-0.00000663973566262036</v>
       </c>
       <c r="U28" t="n">
+        <v>0.00000492750380200972</v>
+      </c>
+      <c r="V28" t="n">
         <v>-0.000000493767469563009</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>-0.025663861124394</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>-0.017873750459558</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>-0.137986254005846</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>-0.021975198682064</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>0.010616105870294</v>
       </c>
-      <c r="AA28" t="n">
-        <v>-0.187131589489871</v>
-      </c>
       <c r="AB28" t="n">
-        <v>-0.176001400416046</v>
+        <v>-0.182861270315215</v>
       </c>
       <c r="AC28" t="n">
+        <v>-0.171743011407605</v>
+      </c>
+      <c r="AD28" t="n">
         <v>0.010525986148044</v>
       </c>
-      <c r="AD28" t="n">
-        <v>-0.335962853103956</v>
-      </c>
       <c r="AE28" t="n">
-        <v>-0.106649814636195</v>
+        <v>-0.331704464095515</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.112723777459433</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
@@ -9688,42 +9979,45 @@
         <v>-0.00000365982582365993</v>
       </c>
       <c r="U29" t="n">
+        <v>0.00000998248410471157</v>
+      </c>
+      <c r="V29" t="n">
         <v>-0.000000457030036575968</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>-0.0243140219475805</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>-0.0186601329074988</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>0.021717113748371</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>-0.021259179791528</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>0.013167795030125</v>
       </c>
-      <c r="AA29" t="n">
-        <v>-0.184063589099885</v>
-      </c>
       <c r="AB29" t="n">
-        <v>-0.171001472523139</v>
+        <v>-0.175414838257923</v>
       </c>
       <c r="AC29" t="n">
+        <v>-0.162348445104158</v>
+      </c>
+      <c r="AD29" t="n">
         <v>0.013228275511513</v>
       </c>
-      <c r="AD29" t="n">
-        <v>-0.170543538566296</v>
-      </c>
       <c r="AE29" t="n">
-        <v>-0.163766288437296</v>
+        <v>-0.161890511147315</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.161618366942589</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
@@ -9781,42 +10075,45 @@
         <v>-0.00000205804904017002</v>
       </c>
       <c r="U30" t="n">
+        <v>0.00000274583479885002</v>
+      </c>
+      <c r="V30" t="n">
         <v>-0.000000422937653624046</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>-0.0229694176276538</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>-0.00285370938537124</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>0.021544796224536</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>-0.021038600092909</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>0.014059878040393</v>
       </c>
-      <c r="AA30" t="n">
-        <v>-0.156539576349319</v>
-      </c>
       <c r="AB30" t="n">
-        <v>-0.143370114188438</v>
+        <v>-0.154163449981375</v>
       </c>
       <c r="AC30" t="n">
+        <v>-0.140980918624873</v>
+      </c>
+      <c r="AD30" t="n">
         <v>0.014368628454244</v>
       </c>
-      <c r="AD30" t="n">
-        <v>-0.142863918056811</v>
-      </c>
       <c r="AE30" t="n">
-        <v>-0.202211865914934</v>
+        <v>-0.140474722493246</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.199155992733798</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
@@ -9874,42 +10171,45 @@
         <v>-0.00000173178208568987</v>
       </c>
       <c r="U31" t="n">
+        <v>-0.000000374545117222012</v>
+      </c>
+      <c r="V31" t="n">
         <v>-0.000000368304749786001</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.000302446729033103</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>-0.0019241092321893</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>0.020896923617158</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>-0.02047790431963</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>0.013899060902457</v>
       </c>
-      <c r="AA31" t="n">
-        <v>-0.0348615039292884</v>
-      </c>
       <c r="AB31" t="n">
-        <v>-0.021147004965466</v>
+        <v>-0.0351856094192511</v>
       </c>
       <c r="AC31" t="n">
+        <v>-0.02147272648154</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.014320024476268</v>
       </c>
-      <c r="AD31" t="n">
-        <v>-0.020727985667938</v>
-      </c>
       <c r="AE31" t="n">
-        <v>-0.167524573848749</v>
+        <v>-0.021053707184012</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.163780851230022</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
@@ -9967,42 +10267,45 @@
         <v>-0.00000143132854011989</v>
       </c>
       <c r="U32" t="n">
+        <v>0.00000582581743696978</v>
+      </c>
+      <c r="V32" t="n">
         <v>-0.000000361016548926013</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.000971336169638</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.000892915220866698</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>0.020377539263201</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>-0.019926752078143</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.013174269440989</v>
       </c>
-      <c r="AA32" t="n">
-        <v>-0.0646973180965704</v>
-      </c>
       <c r="AB32" t="n">
-        <v>-0.05169549196756</v>
+        <v>-0.0596516905208886</v>
       </c>
       <c r="AC32" t="n">
+        <v>-0.046636633358349</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.013621403079999</v>
       </c>
-      <c r="AD32" t="n">
-        <v>-0.051244704782501</v>
-      </c>
       <c r="AE32" t="n">
-        <v>-0.096345036768386</v>
+        <v>-0.0461858461732909</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.092401196749466</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
@@ -10060,42 +10363,45 @@
         <v>-0.000000277565447452991</v>
       </c>
       <c r="U33" t="n">
+        <v>0.00000455777448927011</v>
+      </c>
+      <c r="V33" t="n">
         <v>-0.000000353308630074</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.0564463827973993</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.0003261752991603</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>0.020275240863507</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>-0.019447615728967</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.00232512474688001</v>
       </c>
-      <c r="AA33" t="n">
-        <v>0.0244190184156022</v>
-      </c>
       <c r="AB33" t="n">
-        <v>0.022158396871655</v>
+        <v>0.0283638821477732</v>
       </c>
       <c r="AC33" t="n">
+        <v>0.026113714512556</v>
+      </c>
+      <c r="AD33" t="n">
         <v>-0.00182903357757699</v>
       </c>
-      <c r="AD33" t="n">
-        <v>0.022986022006195</v>
-      </c>
       <c r="AE33" t="n">
-        <v>-0.0479626466252621</v>
+        <v>0.026941339647096</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.0451932340508631</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34"/>
       <c r="C34" t="n">
@@ -10153,37 +10459,40 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>-0.000000346295835988004</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.110941419932264</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>0.00168948108701047</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>0.020082911673997</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>-0.019071706101937</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>-0.00768500934344607</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>0.0638190536725284</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>0.056535151911518</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>-0.0069710195181018</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>0.0575463574835799</v>
       </c>
-      <c r="AE34" t="n">
-        <v>0.00213992225983406</v>
+      <c r="AF34" t="n">
+        <v>0.00431203594334206</v>
       </c>
     </row>
   </sheetData>
